--- a/data/products_master.xlsx
+++ b/data/products_master.xlsx
@@ -505,12 +505,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Drying of solvents, gases, cracked gas, air dehydration</t>
+          <t>Solvent drying, air dehydration, cracked gas polishing</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aperture 3Å, high crush strength, low water adsorption</t>
+          <t>Aperture 3Å; high crush strength; low water uptake</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Natural gas drying, insulation air, dehydration, oxygen PSA</t>
+          <t>Natural gas drying, air dehydration, oxygen PSA, insulation air</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aperture 4Å, superior adsorption capacity</t>
+          <t>Aperture 4Å; strong adsorption capacity; stable bead structure</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Hydrocarbon separation, hydrogen purification, LPG dehydration</t>
+          <t>Hydrocarbon separation, hydrogen purification, LPG drying</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aperture 5Å, selective adsorption for n-paraffins</t>
+          <t>Aperture 5Å; selective adsorption for n-paraffins; stable adsorption profile</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -616,12 +616,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Moisture and CO2 removal, air separation, hydrogen drying</t>
+          <t>CO2 removal, gas drying, hydrogen treatment, air separation</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aperture 10Å, high capacity for polar compounds</t>
+          <t>Aperture 10Å; high adsorption capacity for polar compounds and moisture</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -653,12 +653,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Drying compressed air, fluoride removal, dehydration of gases and liquids</t>
+          <t>Compressed air drying, fluoride removal, hydrogen and natural gas dehydration</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>High surface area, low dust, high crush strength</t>
+          <t>High surface area; low dust; high crush strength; broad adsorption range</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Water purification, odor control, solvent recovery, dechlorination</t>
+          <t>Water purification, dechlorination, odor control, solvent recovery</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Iodine value, mesh size, ash content</t>
+          <t>Iodine value, mesh size, ash content, adsorption profile</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Packaging, compressed air, transformer protection, moisture control</t>
+          <t>Packaging protection, compressed air drying, transformer protection, moisture control</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>High adsorption capacity at low humidity</t>
+          <t>High low-humidity adsorption capacity; stable bead or granule form</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Bleaching efficiency, moisture, oil retention</t>
+          <t>Bleaching efficiency, moisture, oil retention, particle size distribution</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Wastewater clarification, suspended solids removal</t>
+          <t>Wastewater clarification, suspended solids removal, process water conditioning</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Clear liquor, stable supply, low dosage efficiency</t>
+          <t>Stable liquor, consistent dosage efficiency, strong clarification performance</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -838,12 +838,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Softening, demineralization, boiler feed treatment</t>
+          <t>Softening, demineralization, boiler feed water treatment</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Uniform bead size, exchange capacity</t>
+          <t>Uniform bead size, exchange capacity, low fines, process stability</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>RO pretreatment, cooling tower, boiler water treatment</t>
+          <t>RO pretreatment, cooling tower treatment, boiler water stabilization</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Dosage optimization, compatibility</t>
+          <t>Dosage optimization, compatibility, scale suppression performance</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Ceramic Balls, Raschig Rings, Catalysts</t>
+          <t>Ceramic Balls, Raschig Rings, Catalyst Support Media</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Mass transfer, support layers, catalyst bed support</t>
+          <t>Mass transfer, support layers, catalyst bed support, structural media</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Hardness, size distribution, void ratio</t>
+          <t>Hardness, size distribution, void ratio, load-bearing strength</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">

--- a/data/products_master.xlsx
+++ b/data/products_master.xlsx
@@ -434,505 +434,2960 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Family</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Subcategory</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Applications</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Typical Spec</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Grades / Forms</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Image File</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Family</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subcategory</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slug</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Applications</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Typical Spec</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grades / Forms</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Overview</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technical Notes</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documentation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Datasheet</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Image File</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Company Image</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEO Title</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meta Description</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Image Alt</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Adsorbents</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Molecular Sieves</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Molecular Sieve 3A</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Solvent drying, air dehydration, cracked gas polishing</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Aperture 3Å; high crush strength; low water uptake</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Beads, pellets</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>assets/images/molecular-sieve-3a.svg</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adsorbents</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Carbon – Granular (GAC)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Carbon – Granular (GAC)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">activated-carbon-granular-gac</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organic removal, chlorine, colour, odour, pesticides, THMs; solvent recovery; air purification; gold recovery</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coal-based, Coconut-shell, Wood-based; various mesh (4x8, 8x30, 12x40 etc.); different IV grades</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules / Bags / Bulk</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Carbon – Granular (GAC) is supplied for organic removal, chlorine, colour, odour, pesticides, thms; solvent recovery; air purification; gold recovery.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Municipal &amp; Industrial Water Treatment, RO Pre-treatment, Pharma, F&amp;B, Gold mining, Air filters. Highest volume, easiest sales, universal demand. Must-have hero product.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/activated-carbon.svg</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Carbon – Granular (GAC) | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Carbon – Granular (GAC) for organic removal, chlorine, colour, odour, pesticides, thms; solvent recovery; air purification; gold recovery. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Carbon – Granular (GAC) for industrial applications</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Adsorbents</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Molecular Sieves</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Molecular Sieve 4A</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Natural gas drying, air dehydration, oxygen PSA, insulation air</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Aperture 4Å; strong adsorption capacity; stable bead structure</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Beads, pellets</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>assets/images/molecular-sieve-4a.svg</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adsorbents</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Carbon – Powdered (PAC)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Carbon – Powdered (PAC)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">activated-carbon-powdered-pac</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rapid adsorption of organics, colour, taste in liquid phase (dosing systems)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coal / Coconut / Wood based</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Powder / Bags</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Carbon – Powdered (PAC) is supplied for rapid adsorption of organics, colour, taste in liquid phase (dosing systems).</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Water treatment plants, Sugar mills, Pharma, Textile/Dye, Juice &amp; Soft drink plants. High consumption, continuous dosing = excellent repeat. Easy add-on to GAC customers.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/activated-carbon.svg</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Carbon – Powdered (PAC) | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Carbon – Powdered (PAC) for rapid adsorption of organics, colour, taste in liquid phase (dosing systems). Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Carbon – Powdered (PAC) for industrial applications</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Adsorbents</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Molecular Sieves</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Molecular Sieve 5A</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Hydrocarbon separation, hydrogen purification, LPG drying</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Aperture 5Å; selective adsorption for n-paraffins; stable adsorption profile</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Beads, pellets</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>assets/images/molecular-sieve-5a.svg</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adsorbents</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Alumina</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Alumina</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">activated-alumina</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defluoridation, Arsenic removal, Gas &amp; liquid drying, Catalyst support</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balls / Granules (2-5mm, 3-5mm, 5-8mm common); different surface area grades</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balls / Granules</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Alumina is supplied for defluoridation, arsenic removal, gas &amp; liquid drying, catalyst support.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Drinking water (fluoride endemic zones – Rajasthan, UP, Haryana, Gujarat), Industrial gas drying, Petrochemical, Pharma packaging. Strong government + private demand in North India fluoride belt. Excellent technical story.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/activated-alumina.svg</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Alumina | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Alumina for defluoridation, arsenic removal, gas &amp; liquid drying, catalyst support. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Alumina for industrial applications</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Adsorbents</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Molecular Sieves</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Molecular Sieve 13X</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>CO2 removal, gas drying, hydrogen treatment, air separation</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Aperture 10Å; high adsorption capacity for polar compounds and moisture</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Beads, pellets</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>assets/images/molecular-sieve-13x.svg</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adsorbents</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Molecular Sieves (Zeolite)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Molecular Sieves (Zeolite)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molecular-sieves-zeolite</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selective gas drying &amp; separation (H2O, CO2, H2S), PSA Oxygen/Nitrogen generation, Solvent drying, Air separation</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3A, 4A, 5A, 13X, 13X HP, 13X APG; Beads &amp; Powder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beads (1.6-2.5mm, 3-5mm) / Powder</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Molecular Sieves (Zeolite) is supplied for selective gas drying &amp; separation (h2o, co2, h2s), psa oxygen/nitrogen generation, solvent drying, air separation.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: City Gas Distribution (CGD), Oil &amp; Gas, Petrochemical, Pharma, Industrial gas plants, Air separation units, PSA O2 plants. Highest strategic value. CGD expansion + PSA growth in India. Spec-driven selling (crush strength, capacity).</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/molecular-sieve-13x.svg</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Molecular Sieves (Zeolite) | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Molecular Sieves (Zeolite) for selective gas drying &amp; separation (h2o, co2, h2s), psa oxygen/nitrogen generation, solvent drying, air separation. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Molecular Sieves (Zeolite) for industrial applications</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Adsorbents</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Activated Alumina</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Activated Alumina</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Compressed air drying, fluoride removal, hydrogen and natural gas dehydration</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>High surface area; low dust; high crush strength; broad adsorption range</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Granules, pellets</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>assets/images/activated-alumina.svg</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adsorbents</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Silica Gel</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Silica Gel</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">silica-gel</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moisture adsorption (desiccant), Chromatography, Catalyst support, Packaging protection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">White / Blue / Orange indicating; Beads / Powder; B-type, Macro-pore, Oil bleaching, PSA, Water-resistant, Silica-Alumina gel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beads / Powder / Packs</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Silica Gel is supplied for moisture adsorption (desiccant), chromatography, catalyst support, packaging protection.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Pharma packaging, Electronics, Transformer oil, Food packaging, Industrial drying, Labs. Steady demand from pharma &amp; electronics. Indicating grades good for packaging.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/silica-gel.svg</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Silica Gel | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Silica Gel for moisture adsorption (desiccant), chromatography, catalyst support, packaging protection. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Silica Gel for industrial applications</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Adsorbents</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Activated Carbon</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>GAC / PAC</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Water purification, dechlorination, odor control, solvent recovery</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Iodine value, mesh size, ash content, adsorption profile</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Granular, powder</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>assets/images/activated-carbon.svg</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter &amp; Specialty Media</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anthracite</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anthracite</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anthracite</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suspended solids &amp; turbidity removal (top layer in multi-media filters)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Various grades for multi-media filters</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anthracite is supplied for suspended solids &amp; turbidity removal (top layer in multi-media filters).</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Water treatment plants (pressure sand &amp; multi-media), Industrial cooling water, Municipal plants. Essential filter media. Always sold with sand/gravel.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anthracite | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anthracite for suspended solids &amp; turbidity removal (top layer in multi-media filters). Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anthracite for industrial applications</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Adsorbents</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Silica Gel</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Silica Gel Desiccant</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Packaging protection, compressed air drying, transformer protection, moisture control</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>High low-humidity adsorption capacity; stable bead or granule form</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Beads, granules</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>assets/images/silica-gel.svg</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter &amp; Specialty Media</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter Sand (Silica Sand)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter Sand (Silica Sand)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">filter-sand-silica-sand</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turbidity &amp; suspended solids filtration</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Various mesh sizes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter Sand (Silica Sand) is supplied for turbidity &amp; suspended solids filtration.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: All water treatment plants, Swimming pools, Pre-treatment for RO/UF. Commodity but gateway product. High volume.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter Sand (Silica Sand) | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter Sand (Silica Sand) for turbidity &amp; suspended solids filtration. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter Sand (Silica Sand) for industrial applications</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Adsorbents</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Specialty Media</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Bleaching Earth</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Edible oil refining, decolorization, wax polishing</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Bleaching efficiency, moisture, oil retention, particle size distribution</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Powder, granules</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>assets/images/bleaching-earth.svg</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter &amp; Specialty Media</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter Gravel / Support Gravel</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter Gravel / Support Gravel</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">filter-gravel-support-gravel</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support bed for sand / anthracite filters</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Various sizes</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter Gravel / Support Gravel is supplied for support bed for sand / anthracite filters.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Every multi-media or sand filter installation. Must-have accessory. Never sell sand without offering gravel.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter Gravel / Support Gravel | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter Gravel / Support Gravel for support bed for sand / anthracite filters. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter Gravel / Support Gravel for industrial applications</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Water Treatment</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Coagulants &amp; Flocculants</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>PAC / Alum / Ferric</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Wastewater clarification, suspended solids removal, process water conditioning</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Stable liquor, consistent dosage efficiency, strong clarification performance</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Liquid, powder</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>assets/images/coagulants-flocculants.svg</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter &amp; Specialty Media</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garnet</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garnet</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garnet</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bottom layer in advanced multi-media filters</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dense media grades</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garnet is supplied for bottom layer in advanced multi-media filters.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Advanced multi-media filters in industrial &amp; municipal plants. Upsell for higher performance systems.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garnet | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garnet for bottom layer in advanced multi-media filters. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garnet for industrial applications</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Water Treatment</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Ion Exchange</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Strong Acid Cation / Anion Resins</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Softening, demineralization, boiler feed water treatment</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Uniform bead size, exchange capacity, low fines, process stability</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Beads</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>assets/images/ion-exchange.svg</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter &amp; Specialty Media</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Birm Media</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Birm Media</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">birm-media</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catalytic oxidation &amp; removal of dissolved Iron and Manganese (no chemicals if DO present)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard Birm</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Birm Media is supplied for catalytic oxidation &amp; removal of dissolved iron and manganese (no chemicals if do present).</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Borewell / well water treatment, Residential &amp; commercial iron removal filters, Industrial process water, Municipal (iron-affected areas). Very strong demand across North India (iron-affected groundwater). Excellent residential + commercial channel.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Birm Media | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Birm Media for catalytic oxidation &amp; removal of dissolved iron and manganese (no chemicals if do present). Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Birm Media for industrial applications</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Water Treatment</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Antiscalants / Process Chemicals</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Antiscalants, scale inhibitors</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>RO pretreatment, cooling tower treatment, boiler water stabilization</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Dosage optimization, compatibility, scale suppression performance</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Liquid, powder</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>assets/images/antiscalants.svg</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter &amp; Specialty Media</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manganese Greensand / Greensand Plus</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manganese Greensand / Greensand Plus</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganese-greensand-greensand-plus</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iron, Manganese, Hydrogen Sulphide removal (requires KMnO4 regeneration)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard &amp; Plus grades</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manganese Greensand / Greensand Plus is supplied for iron, manganese, hydrogen sulphide removal (requires kmno4 regeneration).</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Same as Birm – higher Fe/Mn loads; Industrial &amp; municipal water treatment. Complement to Birm for tougher water chemistry.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manganese Greensand / Greensand Plus | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manganese Greensand / Greensand Plus for iron, manganese, hydrogen sulphide removal (requires kmno4 regeneration). Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manganese Greensand / Greensand Plus for industrial applications</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Process Media</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Tower Packings &amp; Support Media</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Ceramic Balls, Raschig Rings, Catalyst Support Media</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Mass transfer, support layers, catalyst bed support, structural media</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Hardness, size distribution, void ratio, load-bearing strength</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Ceramic, metal, plastic</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>assets/images/catalyst-support.svg</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter &amp; Specialty Media</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katalox Light / Filox / Pyrolox / MnO2-based Media</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katalox Light / Filox / Pyrolox / MnO2-based Media</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">katalox-light-filox-pyrolox-mno2-based-media</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High-capacity Fe, Mn, H2S, Arsenic, heavy metals removal</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Various MnO2 media brands</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katalox Light / Filox / Pyrolox / MnO2-based Media is supplied for high-capacity fe, mn, h2s, arsenic, heavy metals removal.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Premium iron removal systems, Industrial water, High-contamination borewells. Higher margin premium alternative.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katalox Light / Filox / Pyrolox / MnO2-based Media | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katalox Light / Filox / Pyrolox / MnO2-based Media for high-capacity fe, mn, h2s, arsenic, heavy metals removal. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katalox Light / Filox / Pyrolox / MnO2-based Media for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter &amp; Specialty Media</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calcite / Corosex / MgO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calcite / Corosex / MgO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">calcite-corosex-mgo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pH correction (raises pH), acid water neutralization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pH correction media</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules / Chips</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calcite / Corosex / MgO is supplied for ph correction (raises ph), acid water neutralization.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Acidic water treatment plants, Borewell water (low pH areas), Softener pre-treatment. Easy add-on product.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calcite / Corosex / MgO | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calcite / Corosex / MgO for ph correction (raises ph), acid water neutralization. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calcite / Corosex / MgO for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter &amp; Specialty Media</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter-Ag / Filter-Ag Plus / Clinoptilolite Zeolite</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter-Ag / Filter-Ag Plus / Clinoptilolite Zeolite</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">filter-ag-filter-ag-plus-clinoptilolite-zeolite</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turbidity &amp; suspended solids (lighter than sand, higher dirt holding); some ion exchange</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lightweight media &amp; natural zeolite</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter-Ag / Filter-Ag Plus / Clinoptilolite Zeolite is supplied for turbidity &amp; suspended solids (lighter than sand, higher dirt holding); some ion exchange.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Pressure filters, Industrial water, Swimming pools; Zeolite also for ammonia etc.. Differentiation media + natural zeolite applications.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter-Ag / Filter-Ag Plus / Clinoptilolite Zeolite | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter-Ag / Filter-Ag Plus / Clinoptilolite Zeolite for turbidity &amp; suspended solids (lighter than sand, higher dirt holding); some ion exchange. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter-Ag / Filter-Ag Plus / Clinoptilolite Zeolite for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adsorbents</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bleaching Earth / Activated Clay / Fuller's Earth</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bleaching Earth / Activated Clay / Fuller's Earth</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bleaching-earth-activated-clay-fuller-s-earth</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decolourisation and purification of edible oils, fats, petroleum products</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Various activation grades</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Powder / Granules</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bleaching Earth / Activated Clay / Fuller's Earth is supplied for decolourisation and purification of edible oils, fats, petroleum products.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Edible oil refineries (huge in India), Soap industry, Petroleum refining. Strong volume potential if you can reach oil refineries / soap units.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/bleaching-earth.svg</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bleaching Earth / Activated Clay / Fuller's Earth | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bleaching Earth / Activated Clay / Fuller's Earth for decolourisation and purification of edible oils, fats, petroleum products. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bleaching Earth / Activated Clay / Fuller's Earth for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adsorbents</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bone Char</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bone Char</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bone-char</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fluoride and heavy metal removal; Sugar decolourisation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard bone char</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bone Char is supplied for fluoride and heavy metal removal; sugar decolourisation.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Sugar industry, Specialty water treatment (fluoride). Niche but high value in specific applications.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bone Char | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bone Char for fluoride and heavy metal removal; sugar decolourisation. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bone Char for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adsorbents</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impregnated Activated Carbon</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impregnated Activated Carbon</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">impregnated-activated-carbon</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Specific gas adsorption (H2S, Mercury, Radioactive Iodine, acidic/basic gases)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KOH, KI, Ag, Sulphur, etc. impregnated</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impregnated Activated Carbon is supplied for specific gas adsorption (h2s, mercury, radioactive iodine, acidic/basic gases).</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Air purification, Nuclear, Gold mining, Chemical plants, Odour control. High-value specialty upsell on base GAC customers.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/activated-carbon.svg</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impregnated Activated Carbon | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impregnated Activated Carbon for specific gas adsorption (h2s, mercury, radioactive iodine, acidic/basic gases). Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impregnated Activated Carbon for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adsorbents</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polymeric Adsorbents</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polymeric Adsorbents</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">polymeric-adsorbents</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selective removal of organics, colour, phenol, antibiotics from process streams</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purolite PAD, Amberlite type, etc.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beads</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polymeric Adsorbents is supplied for selective removal of organics, colour, phenol, antibiotics from process streams.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Pharma API plants, Fine chemicals, Food processing, High-value wastewater organics recovery. High margin, high technical. Good after pharma contacts.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polymeric Adsorbents | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polymeric Adsorbents for selective removal of organics, colour, phenol, antibiotics from process streams. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polymeric Adsorbents for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adsorbents</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Bentonite / Organoclay</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Bentonite / Organoclay</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">activated-bentonite-organoclay</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oil &amp; grease removal, heavy metals, organic contaminants</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard &amp; organophilic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Powder / Granules</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Bentonite / Organoclay is supplied for oil &amp; grease removal, heavy metals, organic contaminants.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Industrial wastewater (ETP), Oil spill, Foundry. Useful ETP add-on.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/bleaching-earth.svg</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Bentonite / Organoclay | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Bentonite / Organoclay for oil &amp; grease removal, heavy metals, organic contaminants. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activated Bentonite / Organoclay for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adsorbents</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centaur / Catalytic Carbon</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centaur / Catalytic Carbon</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">centaur-catalytic-carbon</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chloramine, H2S, Iron/Manganese (catalytic performance)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catalytic activated carbon</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centaur / Catalytic Carbon is supplied for chloramine, h2s, iron/manganese (catalytic performance).</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Advanced water systems needing catalytic action. Premium alternative to standard GAC for specific contaminants.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/activated-carbon.svg</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centaur / Catalytic Carbon | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centaur / Catalytic Carbon for chloramine, h2s, iron/manganese (catalytic performance). Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centaur / Catalytic Carbon for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adsorbents</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KDF Media (55/85)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KDF Media (55/85)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kdf-media-55-85</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heavy metals, Chlorine, Bacteria control</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Copper-Zinc media</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KDF Media (55/85) is supplied for heavy metals, chlorine, bacteria control.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Point-of-use filters, Residential &amp; commercial systems, some industrial. Strong dealer / assembler channel potential.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KDF Media (55/85) | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KDF Media (55/85) for heavy metals, chlorine, bacteria control. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KDF Media (55/85) for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ion Exchange</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ion Exchange Resins</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ion Exchange Resins</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ion-exchange-resins</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Softening, Demineralisation, Deionisation, Heavy metal removal</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cation, Anion, Mixed Bed, Chelating resins</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beads / Bags or Drums</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ion Exchange Resins is supplied for softening, demineralisation, deionisation, heavy metal removal.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Boiler feed water, Pharma (WFI/purified water), Electronics, Power plants, Food, Metal finishing. High value, recurring (resin life + regeneration). Strong in NCR pharma + power + boilers.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/ion-exchange.svg</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ion Exchange Resins | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ion Exchange Resins for softening, demineralisation, deionisation, heavy metal removal. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ion Exchange Resins for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ion Exchange</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resin Regeneration Chemicals</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resin Regeneration Chemicals</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resin-regeneration-chemicals</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regeneration of ion exchange resins</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HCl, NaOH, NaCl, etc.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquid / Bags</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resin Regeneration Chemicals is supplied for regeneration of ion exchange resins.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: All users of IX resins (boilers, DM plants, pharma). Natural cross-sell. Never sell resin without offering regen chemicals option.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/ion-exchange.svg</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resin Regeneration Chemicals | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resin Regeneration Chemicals for regeneration of ion exchange resins. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resin Regeneration Chemicals for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coagulants &amp; Flocculants</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyaluminium Chloride (PAC)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyaluminium Chloride (PAC)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">polyaluminium-chloride-pac</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primary coagulant for turbidity, colour, organics removal in water &amp; wastewater</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquid &amp; Powder; different basicity grades; also Polymer Aluminium Ferric Chloride</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquid / Powder</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyaluminium Chloride (PAC) is supplied for primary coagulant for turbidity, colour, organics removal in water &amp; wastewater.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Municipal water treatment, Industrial ETP, Paper, Textile, etc.. One of the highest volume coagulants in India. Excellent repeat.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/coagulants-flocculants.svg</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyaluminium Chloride (PAC) | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyaluminium Chloride (PAC) for primary coagulant for turbidity, colour, organics removal in water &amp; wastewater. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyaluminium Chloride (PAC) for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coagulants &amp; Flocculants</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyacrylamide (PAM)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyacrylamide (PAM)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">polyacrylamide-pam</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flocculant for solid-liquid separation, sludge dewatering, enhanced settling</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Powder (Anionic / Cationic / Non-ionic), Emulsion, PHPA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Powder / Emulsion</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyacrylamide (PAM) is supplied for flocculant for solid-liquid separation, sludge dewatering, enhanced settling.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Water treatment, Mining, Oilfield, Paper, Municipal sludge. High consumption flocculant. Technical grade selection important.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/coagulants-flocculants.svg</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyacrylamide (PAM) | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyacrylamide (PAM) for flocculant for solid-liquid separation, sludge dewatering, enhanced settling. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyacrylamide (PAM) for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coagulants &amp; Flocculants</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polydadmac / Polyamine</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polydadmac / Polyamine</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">polydadmac-polyamine</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organic coagulants / flocculants, often used with or instead of metal salts</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Various molecular weights</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquid</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polydadmac / Polyamine is supplied for organic coagulants / flocculants, often used with or instead of metal salts.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Water treatment, Paper, Textile, Oilfield. Growing preference for organic coagulants in some applications.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/coagulants-flocculants.svg</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polydadmac / Polyamine | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polydadmac / Polyamine for organic coagulants / flocculants, often used with or instead of metal salts. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polydadmac / Polyamine for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coagulants &amp; Flocculants</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aluminium based Coagulants</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aluminium based Coagulants</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aluminium-based-coagulants</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coagulation in water treatment</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aluminium Chlorohydrate (ACH), Aluminium Sulfate (Alum), Crystalline Aluminium Chloride</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Powder / Liquid / Crystals</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aluminium based Coagulants is supplied for coagulation in water treatment.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Municipal &amp; Industrial water treatment. Traditional and still widely used. Alum is classic.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/coagulants-flocculants.svg</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aluminium based Coagulants | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aluminium based Coagulants for coagulation in water treatment. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aluminium based Coagulants for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coagulants &amp; Flocculants</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iron based Coagulants</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iron based Coagulants</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iron-based-coagulants</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coagulation, especially effective for phosphorus &amp; some organics; also sludge conditioning</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ferric Chloride, Ferric Sulphate, Polymerized Ferrous Sulfate</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquid / Powder</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iron based Coagulants is supplied for coagulation, especially effective for phosphorus &amp; some organics; also sludge conditioning.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Municipal wastewater, Industrial ETP, Phosphorus removal. Strong in wastewater applications.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/coagulants-flocculants.svg</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iron based Coagulants | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iron based Coagulants for coagulation, especially effective for phosphorus &amp; some organics; also sludge conditioning. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iron based Coagulants for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting Water Chemicals</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other Coagulant / Treatment Chemicals</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other Coagulant / Treatment Chemicals</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other-coagulant-treatment-chemicals</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pH adjustment, dechlorination, specific treatment needs</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Magnesium Chloride, Calcium Chloride, Sodium Metabisulfite, Sodium Bicarbonate, Sodium Hydroxide, AMPS, etc.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Various</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other Coagulant / Treatment Chemicals is supplied for ph adjustment, dechlorination, specific treatment needs.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Various water treatment processes. Useful supporting chemicals once you are supplying main coagulants/adsorbents.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/coagulants-flocculants.svg</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other Coagulant / Treatment Chemicals | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other Coagulant / Treatment Chemicals for ph adjustment, dechlorination, specific treatment needs. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other Coagulant / Treatment Chemicals for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting Water Chemicals</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defoamer / Antifoam</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defoamer / Antifoam</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defoamer-antifoam</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foam control in treatment processes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Various silicone / non-silicone</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquid</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defoamer / Antifoam is supplied for foam control in treatment processes.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: ETP, Process plants. Common need in many plants.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defoamer / Antifoam | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defoamer / Antifoam for foam control in treatment processes. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Defoamer / Antifoam for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas Treatment Media</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hopcalite Catalyst</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hopcalite Catalyst</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hopcalite-catalyst</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO oxidation / removal at ambient or low temperature</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hopcalite type</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granules / Pellets</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hopcalite Catalyst is supplied for co oxidation / removal at ambient or low temperature.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Air purification, Safety, some industrial gas treatment. Useful specialty for gas treatment portfolio.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/catalyst-support.svg</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hopcalite Catalyst | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hopcalite Catalyst for co oxidation / removal at ambient or low temperature. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hopcalite Catalyst for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas Treatment Media</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO Removal Catalysts</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO Removal Catalysts</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">co-removal-catalysts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carbon monoxide removal from gas streams</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pt/Pd based, Ceramic honeycomb, others</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Various forms</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO Removal Catalysts is supplied for carbon monoxide removal from gas streams.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Industrial gas purification, Emission control, Safety systems. Selective – only common grades. High technical barrier for advanced ones.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/catalyst-support.svg</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO Removal Catalysts | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO Removal Catalysts for carbon monoxide removal from gas streams. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO Removal Catalysts for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas Treatment Media</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ozone Decomposition / Removal Catalysts &amp; Filters</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ozone Decomposition / Removal Catalysts &amp; Filters</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ozone-decomposition-removal-catalysts-filters</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ozone destruction in off-gas or process streams</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ozone decomposition catalyst, Copper mesh carrier filters</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catalyst / Filter media</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ozone Decomposition / Removal Catalysts &amp; Filters is supplied for ozone destruction in off-gas or process streams.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Water treatment (ozone systems), Industrial processes using ozone. Relevant as ozone use grows in water treatment.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/catalyst-support.svg</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ozone Decomposition / Removal Catalysts &amp; Filters | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ozone Decomposition / Removal Catalysts &amp; Filters for ozone destruction in off-gas or process streams. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ozone Decomposition / Removal Catalysts &amp; Filters for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas Treatment Media</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOCs Catalyst / Copper Oxide Catalyst / Iron Oxide Desulfurizers / CO2 Absorbent</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOCs Catalyst / Copper Oxide Catalyst / Iron Oxide Desulfurizers / CO2 Absorbent</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vocs-catalyst-copper-oxide-catalyst-iron-oxide-desulfurizers-co2-absorbent</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOC oxidation, Desulfurization, CO2 removal</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Various</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Various</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOCs Catalyst / Copper Oxide Catalyst / Iron Oxide Desulfurizers / CO2 Absorbent is supplied for voc oxidation, desulfurization, co2 removal.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Air pollution control, Gas purification, Biogas, etc.. Selective entry based on actual inquiries. Do not overload initial range.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/catalyst-support.svg</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOCs Catalyst / Copper Oxide Catalyst / Iron Oxide Desulfurizers / CO2 Absorbent | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOCs Catalyst / Copper Oxide Catalyst / Iron Oxide Desulfurizers / CO2 Absorbent for voc oxidation, desulfurization, co2 removal. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOCs Catalyst / Copper Oxide Catalyst / Iron Oxide Desulfurizers / CO2 Absorbent for industrial applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter &amp; Specialty Media</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ceramic Filter Media / Bio-media</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ceramic Filter Media / Bio-media</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ceramic-filter-media-bio-media</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biological filtration, some physical filtration</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Various ceramic &amp; bio media</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Various</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ceramic Filter Media / Bio-media is supplied for biological filtration, some physical filtration.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target industries: Aquaculture, Wastewater bio-treatment, some industrial. Lower priority for pure adsorption focus, but useful in full water treatment offering.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CoA, TDS and MSDS available on request.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/assets/images/product-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ceramic Filter Media / Bio-media | Aarbutus Technologies</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ceramic Filter Media / Bio-media for biological filtration, some physical filtration. Request technical documentation and a quote from Aarbutus Technologies.</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ceramic Filter Media / Bio-media for industrial applications</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
